--- a/docs/cap-analysis/BridgeManagement_v3.9.33_2026-06-11.xlsx
+++ b/docs/cap-analysis/BridgeManagement_v3.9.33_2026-06-11.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AS 5100, AS5100, Austroads, EPSG, GDA2020, IRAP, ISO 55000, ISO 55001, NHVR, ONRSR, TfNSW</t>
+          <t>AS 5100, AS5100, Austroads, EPSG, GDA2020, IRAP, ISO 55000, ISO 55001, NHVR, ONRSR, state road authority</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inspection evidence captured to TfNSW levels</t>
+          <t>Inspection evidence captured to state road authority levels</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TfNSW (NSW) asset custodianship</t>
+          <t>state road authority (NSW) asset custodianship</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>TfNSW (NSW) asset custodianship</t>
+          <t>state road authority (NSW) asset custodianship</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>AS 5100.7 Table 4 (condition states) / TfNSW 1-5</t>
+          <t>AS 5100.7 Table 4 (condition states) / state road authority 1-5</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Austroads AGBM Part 6 / TfNSW inspection levels 1-3</t>
+          <t>Austroads AGBM Part 6 / state road authority inspection levels 1-3</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>TfNSW (NSW) asset custodianship</t>
+          <t>state road authority (NSW) asset custodianship</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Austroads AGBM Part 6 / TfNSW inspection levels 1-3</t>
+          <t>Austroads AGBM Part 6 / state road authority inspection levels 1-3</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Austroads AGBM Part 6 / TfNSW inspection levels 1-3</t>
+          <t>Austroads AGBM Part 6 / state road authority inspection levels 1-3</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>AS 5100.7 Table 4 (condition states) / TfNSW 1-5</t>
+          <t>AS 5100.7 Table 4 (condition states) / state road authority 1-5</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>AS 5100.7 Table 4 (condition states) / TfNSW 1-5</t>
+          <t>AS 5100.7 Table 4 (condition states) / state road authority 1-5</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inspection evidence captured to TfNSW levels</t>
+          <t>Inspection evidence captured to state road authority levels</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
